--- a/stories/arbres/ATOM-VIV.ANI.003-07.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.003-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Géraldine va au jardin avec papa. Le lapin a soif. Papa, c'est l'adulte. Papa prend le bol. Géraldine tient le bol avec lui. Ils remplissent l'eau, avec un adulte. L'eau cliquette. Géraldine pose le bol. Elle est douce. Sa main va tout doucement. Le lapin s'approche. Géraldine dit : je suis douce. Papa verse aussi un peu de foin. Avec un adulte. Géraldine pose le foin. Elle reste douce. Le lapin croque. Papa dit : on prend soin avec un adulte. On est doux. Géraldine écoute le croquement. Elle sourit.</t>
+          <t>Géraldine va au jardin avec papa. Le lapin a soif. Papa, c'est l'adulte. Papa prend le bol. Géraldine tient le bol avec lui. Ils remplissent l'eau, avec un adulte. L'eau cliquette. Géraldine pose le bol. Elle est douce. Sa main va tout doucement. Le lapin s'approche. Je suis douce. Papa verse aussi un peu de foin. Avec un adulte. Géraldine pose le foin. Elle reste douce. Le lapin croque. On prend soin avec un adulte. On est doux. Géraldine écoute le croquement. Elle sourit.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Géraldine va au jardin avec papa. Le lapin a soif. Papa, c'est l'adulte. Papa prend le bol. Géraldine tient le bol avec lui. Ils remplissent l'eau, avec un adulte. L'eau cliquette. Géraldine pose le bol. Elle est douce. Sa main va tout doucement. Le lapin s'approche.
+enfant-f|Je suis douce. Papa verse aussi un peu de foin. Avec un adulte.
+narrateur|Géraldine pose le foin. Elle reste douce. Le lapin croque.
+papa|On prend soin avec un adulte. On est doux.
+narrateur|Géraldine écoute le croquement. Elle sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1490,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Géraldine donne de l'eau au lapin. Comment fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1663,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Géraldine a rempli l'eau avec un adulte. Elle a été douce. Papa était là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1826,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Le lapin boit. Géraldine recule doucement.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1993,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2033,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-VIV.ANI.003-07.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.003-07.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,7 @@
 narrateur|Géraldine écoute le croquement. Elle sourit.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1497,6 +1503,7 @@
           <t>narrateur|Géraldine donne de l'eau au lapin. Comment fait-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1668,6 +1675,7 @@
           <t>narrateur|Géraldine a rempli l'eau avec un adulte. Elle a été douce. Papa était là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1831,6 +1839,7 @@
           <t>narrateur|Le lapin boit. Géraldine recule doucement.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1998,6 +2007,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2016,7 +2026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2040,6 +2050,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2054,7 +2078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2241,6 +2265,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-VIV.ANI.003-07.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.003-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Géraldine prend soin du lapin avec papa</t>
+          <t>L'oreille à la grille</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Victorino veut soigner le lapin qui a soif. Une oreille passe la grille. Ils restent, tout doux. Le lapin boit.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Géraldine va au jardin avec papa. Le lapin a soif. Papa, c'est l'adulte. Papa prend le bol. Géraldine tient le bol avec lui. Ils remplissent l'eau, avec un adulte. L'eau cliquette. Géraldine pose le bol. Elle est douce. Sa main va tout doucement. Le lapin s'approche. Je suis douce. Papa verse aussi un peu de foin. Avec un adulte. Géraldine pose le foin. Elle reste douce. Le lapin croque. On prend soin avec un adulte. On est doux. Géraldine écoute le croquement. Elle sourit.</t>
+          <t>L'ombre du grillage barre le chemin. Les barres sont longues, toutes bleues. Ça sent le thym du bord, et le foin. Le jour baisse, Victorino. Le lapin a soif. Je veux qu'il boive. On y va ensemble. Les cigales se taisent, une à une. Une dalle est encore chaude sous le pied. En ce moment, Victorino est devant le clapier. Le lapin gris est tout près de la grille. Une oreille passe entre les fils. L'oreille est rose, un peu. Son oreille, papa. On reste ici. On ne tire pas. On est doux. Avec un adulte. Tu vois la gamelle ? Elle est vide. On remplit. Toi le bol, moi l'eau. Victorino tient le bol. Papa verse un filet. Pas trop. L'eau cliquette. Tout doux. On pose près de la grille. Victorino pose le bol. Sa main va lentement. Il ne touche pas l'oreille. Le bol se pose sans bruit. On recule. On reste près de moi. Le lapin rentre l'oreille. Elle glisse, toute seule. Puis il s'approche de l'eau. Il boit. Oui. Les moustaches bougent. L'eau baisse.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Géraldine va au jardin &lt;emphasis level="moderate"&gt;avec&lt;/emphasis&gt; papa. Le lapin a soif. Papa, c'est l'adulte. Papa prend le bol. Géraldine tient le bol avec lui. Ils remplissent l'eau, avec un adulte. L'eau cliquette. Géraldine pose le bol. Elle est douce. Sa main va tout doucement. Le lapin s'approche. Géraldine dit : je suis douce. Papa verse aussi un peu de foin. Avec un adulte. Géraldine pose le foin. Elle reste douce. Le lapin croque. Papa dit : on prend soin avec un adulte. On est doux. Géraldine écoute le croquement. Elle sourit.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>L'ombre du grillage barre le chemin. Les barres sont longues, toutes bleues. Ça sent le thym du bord, et le foin. Le jour baisse, Victorino. Le lapin a soif. Je veux qu'il boive. On y va ensemble. Les cigales se taisent, une à une. Une dalle est encore chaude sous le pied. En ce moment, Victorino est devant le clapier. Le lapin gris est tout près de la grille. Une oreille passe entre les fils. L'oreille est rose, un peu. Son oreille, papa. On reste ici. On ne tire pas. On est doux. Avec un adulte. Tu vois la gamelle ? Elle est vide. On remplit. Toi le bol, moi l'eau. Victorino tient le bol. Papa verse un filet. Pas trop. L'eau cliquette. Tout doux. On pose près de la grille. Victorino pose le bol. Sa main va lentement. Il ne touche pas l'oreille. Le bol se pose sans bruit. On recule. On reste près de moi. Le lapin rentre l'oreille. Elle glisse, toute seule. Puis il s'approche de l'eau. Il boit. Oui. Les moustaches bougent. L'eau baisse.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1240,7 +1252,7 @@
         <v>0.92</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,14 +1324,49 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Géraldine va au jardin avec papa. Le lapin a soif. Papa, c'est l'adulte. Papa prend le bol. Géraldine tient le bol avec lui. Ils remplissent l'eau, avec un adulte. L'eau cliquette. Géraldine pose le bol. Elle est douce. Sa main va tout doucement. Le lapin s'approche.
-enfant-f|Je suis douce. Papa verse aussi un peu de foin. Avec un adulte.
-narrateur|Géraldine pose le foin. Elle reste douce. Le lapin croque.
-papa|On prend soin avec un adulte. On est doux.
-narrateur|Géraldine écoute le croquement. Elle sourit.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|L'ombre du grillage barre le chemin.
+narrateur|Les barres sont longues, toutes bleues.
+narrateur|Ça sent le thym du bord, et le foin.
+papa|Le jour baisse, Victorino.
+enfant-m|Le lapin a soif.
+enfant-m|Je veux qu'il boive.
+papa|On y va ensemble.
+narrateur|Les cigales se taisent, une à une.
+narrateur|Une dalle est encore chaude sous le pied.
+narrateur|En ce moment, Victorino est devant le clapier.
+narrateur|Le lapin gris est tout près de la grille.
+narrateur|Une oreille passe entre les fils.
+narrateur|L'oreille est rose, un peu.
+enfant-m|Son oreille, papa.
+papa|On reste ici.
+papa|On ne tire pas.
+papa|On est doux.
+papa|Avec un adulte.
+papa|Tu vois la gamelle ?
+enfant-m|Elle est vide.
+papa|On remplit.
+papa|Toi le bol, moi l'eau.
+narrateur|Victorino tient le bol.
+narrateur|Papa verse un filet.
+narrateur|Pas trop.
+narrateur|L'eau cliquette.
+enfant-m|Tout doux.
+papa|On pose près de la grille.
+narrateur|Victorino pose le bol.
+narrateur|Sa main va lentement.
+narrateur|Il ne touche pas l'oreille.
+narrateur|Le bol se pose sans bruit.
+papa|On recule.
+papa|On reste près de moi.
+narrateur|Le lapin rentre l'oreille.
+narrateur|Elle glisse, toute seule.
+narrateur|Puis il s'approche de l'eau.
+enfant-m|Il boit.
+papa|Oui.
+narrateur|Les moustaches bougent.
+narrateur|L'eau baisse.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1344,12 +1391,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Géraldine donne de l'eau au lapin. Comment fait-elle ?</t>
+          <t>Victorino donne de l'eau au lapin. Comment fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Géraldine donne de l'eau au lapin. Comment fait-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorino donne de l'eau au lapin. Comment fait-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1379,7 +1426,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Papa est là. Elle est douce. Comment fait-elle ?</t>
+          <t>Papa est avec lui. Il est doux. Comment fait-il ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1428,7 +1475,7 @@
         <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1500,10 +1547,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Géraldine donne de l'eau au lapin. Comment fait-elle ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Victorino donne de l'eau au lapin.
+narrateur|Comment fait-il ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1528,12 +1575,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Géraldine a rempli l'eau avec un adulte. Elle a été douce. Papa était là.</t>
+          <t>Le lapin lape encore. L'oreille est rentrée, bien à lui. Elle est rentrée. Toute seule. Tu as été doux. Avec un adulte. Merci, Victorino. Tu as vu l'oreille ? Je n'ai pas tiré. On a donné l'eau. Victorino a les mains dans les poches. Il ne prend pas le lapin. Papa verse aussi un peu de foin. Victorino pose le foin, tout doux. Pour après. Pour croquer, oui. Le lapin boit une dernière goutte. Puis il croque. Il n'a plus soif. Il a bu.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Géraldine a rempli l'eau &lt;emphasis level="moderate"&gt;avec&lt;/emphasis&gt; un adulte. Elle a été douce. Papa était là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le lapin lape encore. L'oreille est rentrée, bien à lui. Elle est rentrée. Toute seule. Tu as été doux. Avec un adulte. Merci, Victorino. Tu as vu l'oreille ? Je n'ai pas tiré. On a donné l'eau. Victorino a les mains dans les poches. Il ne prend pas le lapin. Papa verse aussi un peu de foin. Victorino pose le foin, tout doux. Pour après. Pour croquer, oui. Le lapin boit une dernière goutte. Puis il croque. Il n'a plus soif. Il a bu.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1596,7 +1643,7 @@
         <v>0.92</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1672,10 +1719,28 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Géraldine a rempli l'eau avec un adulte. Elle a été douce. Papa était là.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Le lapin lape encore.
+narrateur|L'oreille est rentrée, bien à lui.
+enfant-m|Elle est rentrée.
+papa|Toute seule.
+papa|Tu as été doux.
+papa|Avec un adulte.
+papa|Merci, Victorino.
+papa|Tu as vu l'oreille ?
+enfant-m|Je n'ai pas tiré.
+papa|On a donné l'eau.
+narrateur|Victorino a les mains dans les poches.
+narrateur|Il ne prend pas le lapin.
+narrateur|Papa verse aussi un peu de foin.
+narrateur|Victorino pose le foin, tout doux.
+enfant-m|Pour après.
+papa|Pour croquer, oui.
+narrateur|Le lapin boit une dernière goutte.
+narrateur|Puis il croque.
+enfant-m|Il n'a plus soif.
+papa|Il a bu.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1700,12 +1765,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Le lapin boit. Géraldine recule doucement.</t>
+          <t>Le jour est presque parti. L'ombre du grillage s'est allongée. Elle touche maintenant les dalles. C'est plus bleu. Le soir arrive. C'était ça, ton envie. Qu'il boive. Victorino s'assoit sur la dalle tiède. Papa s'assoit près de lui. Le thym sent plus fort, le soir. On rentre bientôt ? Encore un peu. Le lapin se lèche la patte. L'oreille rose est bien dedans. Bien rentrée. Oui.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le lapin boit. Géraldine recule doucement.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le jour est presque parti. L'ombre du grillage s'est allongée. Elle touche maintenant les dalles. C'est plus bleu. Le soir arrive. C'était ça, ton envie. Qu'il boive. Victorino s'assoit sur la dalle tiède. Papa s'assoit près de lui. Le thym sent plus fort, le soir. On rentre bientôt ? Encore un peu. Le lapin se lèche la patte. L'oreille rose est bien dedans. Bien rentrée. Oui.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1768,7 +1833,7 @@
         <v>0.92</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1836,10 +1901,24 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Le lapin boit. Géraldine recule doucement.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Le jour est presque parti.
+narrateur|L'ombre du grillage s'est allongée.
+narrateur|Elle touche maintenant les dalles.
+enfant-m|C'est plus bleu.
+papa|Le soir arrive.
+papa|C'était ça, ton envie.
+papa|Qu'il boive.
+narrateur|Victorino s'assoit sur la dalle tiède.
+narrateur|Papa s'assoit près de lui.
+narrateur|Le thym sent plus fort, le soir.
+papa|On rentre bientôt ?
+enfant-m|Encore un peu.
+narrateur|Le lapin se lèche la patte.
+narrateur|L'oreille rose est bien dedans.
+enfant-m|Bien rentrée.
+papa|Oui.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1864,12 +1943,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le lapin a de l'eau. Tout doux, près de la grille. Une cigale fait un dernier chant. Le jardin sent le thym et le foin.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le lapin a de l'eau. Tout doux, près de la grille. Une cigale fait un dernier chant. Le jardin sent le thym et le foin.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1925,14 +2004,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.88</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2004,10 +2083,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>enfant-m|Le lapin a de l'eau.
+papa|Tout doux, près de la grille.
+narrateur|Une cigale fait un dernier chant.
+narrateur|Le jardin sent le thym et le foin.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2026,7 +2107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2064,6 +2145,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-VIV.ANI.003-07.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.003-07.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>jardin, clapier</t>
+          <t>jardin, clapier, fin de journée</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Géraldine, papa</t>
+          <t>Victorino, papa</t>
         </is>
       </c>
     </row>
